--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2405-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2405-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C46C5A96-D2DC-409A-8049-E20700EE52CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3056A290-F38A-4F8D-A549-B8BC48093020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D473530F-2F3F-4E6B-B959-2B6D200933D4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C2B5F462-3321-4294-8FDE-0D7BCFCAE818}"/>
   </bookViews>
   <sheets>
     <sheet name="2405-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,23 +1478,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BCBDBF-C7EC-451A-97CE-17CE9D338337}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BEB3FC-38A8-4B25-A4DF-71AA6C566EB1}">
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1521,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1552,7 +1551,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1648,7 +1647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1702,7 +1701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1812,7 +1811,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1924,7 +1923,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1980,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2034,7 +2033,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2146,7 +2145,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2202,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>2023</v>
       </c>
@@ -2256,7 +2255,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="38">
         <v>2022</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2021</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2020</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2866,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2019</v>
       </c>
@@ -2920,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2976,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2018</v>
       </c>
@@ -3086,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2017</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2016</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2015</v>
       </c>
@@ -3248,7 +3247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2014</v>
       </c>
@@ -3302,7 +3301,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2013</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2012</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2011</v>
       </c>
@@ -3464,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2010</v>
       </c>
@@ -3518,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2009</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2008</v>
       </c>
@@ -3626,7 +3625,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2007</v>
       </c>
@@ -3680,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2006</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2005</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>2004</v>
       </c>
@@ -3842,7 +3841,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>2003</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>2002</v>
       </c>
@@ -3950,7 +3949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>2001</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>2000</v>
       </c>
@@ -4058,7 +4057,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>1999</v>
       </c>
@@ -4112,7 +4111,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>1998</v>
       </c>
@@ -4166,7 +4165,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>1997</v>
       </c>
@@ -4220,7 +4219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>1996</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>1995</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="38">
         <v>1994</v>
       </c>
@@ -4382,7 +4381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="40" t="s">
         <v>44</v>
       </c>
